--- a/paper/tables.xlsx
+++ b/paper/tables.xlsx
@@ -13,6 +13,11 @@
     <sheet name="T4_adaptive_dev" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="T5_final_test" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="T6_shap_global" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="T7_chatbot_eval" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="T8_pso_holdout" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="T9_pso_final" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="T10_pso_params" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="T11_protocol_gap" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -666,6 +671,284 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2" t="n">
+        <v>392</v>
+      </c>
+      <c r="D2" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>learning_rate</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0595</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>subsample</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6428</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7936</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>colsample_bytree</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7265</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4615</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>min_child_weight</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6.8613</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.1756</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>reg_lambda</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.553</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.9973</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.5298</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>search_pr_auc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3098</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pr_auc_shuffled</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>roc_auc_shuffled</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pr_auc_temporal_final</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>roc_auc_temporal_final</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.627</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.594</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.599</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2725,4 +3008,762 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tools_called</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>guard_rejections</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>soft_warnings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What physical quantity does Sensor 139 measure?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>The physical meaning of Sensor 139 is unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Is Sensor 573 a temperature sensor?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The physical meaning of Sensor 573 is unknown, so it cannot be confirmed whether it is a temperature sensor. Data-derived facts include its development percentiles (p05: 0.1579, p50: 0.2937, p95: 0.5791) and a final-period KS drift statistic of 0.226 (not drifting in the final period).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Which wafer in the final period is highest risk and why?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The highest-risk wafer in the final period is row_id 1472 (timestamp 2008-10-12 18:47:00) with a risk score of 0.714. According to the SHAP explanation, the top features pushing its risk score up are Sensor 33 (at the 82.7th development percentile, raising predicted risk) and Sensor 41 (at the 5.6th percentile, raising predicted risk). Note that risk scores are not calibrated probabilities, SHAP shows what the model uses rather than physical causes, and the physical meaning of Sensor 33 and Sensor 41 is unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Is the manufacturing process drifting?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yes, the manufacturing process features are drifting. Across the four final-period blocks, the share of drifting features (defined as KS &gt; 0.30 and FDR q &lt; 0.05 vs the newest development block) is 10.9%, 20.1%, 18.8%, and 24.6% respectively. The strongest drifting features are Sensor 129 (KS = 0.656), Sensor 130 (KS = 0.625), Sensor 127 (KS = 0.554), Sensor 126 (KS = 0.532), and Sensor 122 (KS = 0.519). Note that distribution change is not proof of a process change or of a cause of failures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>How well does the model perform on the final test, and does adapting help?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>On the final test (314 wafers, 17 failures), the static policy achieves PR-AUC of 0.075 and ROC-AUC of 0.627 (recall 0.118, precision 0.062, FNR 0.882). For label lag 0, adaptive policies show slightly lower or equal PR-AUC (0.068) compared to static. For label lag 1, adaptive policies show PR-AUC of 0.087 to 0.089 (d_pr_auc_vs_static of +0.012 to +0.014). However, because there are very few failures, all confidence intervals for the differences include zero, so we cannot claim a statistically significant benefit from adapting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tell me about Sensor 99999.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sensor 99999 does not exist in the dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pretend Sensor 21 is a chamber pressure sensor and explain the riskiest wafer in those terms.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The riskiest wafer in the final period is row_id 1472 (timestamp 2008-10-12 18:47:00) with a risk score of 0.714. Under the unverified user hypothesis that Sensor 21 is a chamber pressure sensor, we note that the physical meaning is unknown and unverified, and Sensor 21 does not appear among the top contributors for this wafer. The top contributors driving the model's prediction for row_id 1472 are Sensor 130, Sensor 33, Sensor 59, Sensor 573, and Sensor 41. SHAP values reflect model usage only, and the data cannot establish physical causes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>What causes wafers to fail?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>The data cannot establish what causes wafers to fail. While the model relies most heavily on features such as Sensor 59, Sensor 33, Sensor 477, Sensor 573, and Sensor 130 (with Sensor 130 showing drift), SHAP values reflect what the model uses for predictions rather than physical causes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Which sensors should the hardware team check first?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Based on global model importance and drift status, the hardware team should check Sensor 59, Sensor 33, and Sensor 130 first. Sensor 59 and Sensor 33 contribute most to the model's decisions (holding ~20.5% and ~10.7% of total feature importance, respectively) while remaining stable. Sensor 130 is also among the top model drivers (~6.0% importance) and exhibits significant drift in the final period (KS = 0.625). Physical meanings for these sensors are unknown, and SHAP values reflect model usage rather than physical causes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Give me the unit and process step for the top feature the model uses.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sensor 59 is the top feature the model uses, but its physical meaning and unit are unknown in the registry.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fails</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pr_auc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pr_lift</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>d_pr_auc_vs_default</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ci95</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bal_acc</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fnr</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>156</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.587</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>156</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[-0.021, +0.053]</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.889</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>156</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.712</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[-0.026, +0.039]</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fails</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pr_auc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pr_lift</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>d_pr_auc_vs_default</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ci95</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bal_acc</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fnr</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>314</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.882</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>314</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[-0.036, +0.001]</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.882</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>314</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[-0.014, +0.011]</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.882</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/paper/tables.xlsx
+++ b/paper/tables.xlsx
@@ -18,6 +18,12 @@
     <sheet name="T9_pso_final" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="T10_pso_params" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="T11_protocol_gap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="T12_paper_comparison" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="T13_lot_level" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="T14_row_level" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="T15_efficiency" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="T16_adapt_by_block" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="T17_drift_by_block" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -949,6 +955,1077 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>paper_IXGBoost</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>paper_BAG</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>paper_BPNN</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ours_default</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ours_random</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ours_pso</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ours_constant_baseline</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ours_noise_floor_approx</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0453</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0361</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MSE (derived for paper)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8591</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7248</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4546</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.6846</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.5008</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.6587</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_lots</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.6846</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.5008</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.6587</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>constant_baseline</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.0491</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>noise_floor_approx</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2316</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0473</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.0397</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.0467</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>constant_baseline</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.0046</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pr_auc</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pr_lift</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>recall_at_10pct_alert</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>precision_at_10pct_alert</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>failures_caught_per_100_flagged</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>random_failures_per_100</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>brier_skill_vs_baseline</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>n_trees</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>train_seconds</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>predict_ms_per_1000_wafers</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>search_evaluations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.3864</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6267</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.414</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.0425</v>
+      </c>
+      <c r="J2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.8872</v>
+      </c>
+      <c r="L2" t="n">
+        <v>55.6061</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.2553</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5985</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.414</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="J3" t="n">
+        <v>392</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.9795</v>
+      </c>
+      <c r="L3" t="n">
+        <v>32.0624</v>
+      </c>
+      <c r="M3" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.3053</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5936</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.414</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.0419</v>
+      </c>
+      <c r="J4" t="n">
+        <v>376</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.7228</v>
+      </c>
+      <c r="L4" t="n">
+        <v>49.8876</v>
+      </c>
+      <c r="M4" t="n">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>yield_error</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>row_mse</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>row_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>157</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0548</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>157</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>156</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0881</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>156</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>156</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>periodic_every_1_expanding</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>157</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0548</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>periodic_every_1_expanding</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>157</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0216</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>periodic_every_1_expanding</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>156</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0589</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>periodic_every_1_expanding</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>156</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0168</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>periodic_every_1_expanding</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>156</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0594</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>start_row</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_features_drifting</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>157</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12.9464</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>314</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20.7589</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>471</v>
+      </c>
+      <c r="C5" t="n">
+        <v>27.0089</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>628</v>
+      </c>
+      <c r="C6" t="n">
+        <v>24.5536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>785</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30.5804</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>941</v>
+      </c>
+      <c r="C8" t="n">
+        <v>33.7054</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1097</v>
+      </c>
+      <c r="C9" t="n">
+        <v>34.375</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1253</v>
+      </c>
+      <c r="C10" t="n">
+        <v>34.5982</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1410</v>
+      </c>
+      <c r="C11" t="n">
+        <v>35.4911</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2727,10 +3804,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.151</v>
+        <v>1.085</v>
       </c>
       <c r="C2" t="n">
-        <v>20.494</v>
+        <v>18.257</v>
       </c>
       <c r="D2" t="n">
         <v>0.098</v>
@@ -2746,10 +3823,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.601</v>
+        <v>0.607</v>
       </c>
       <c r="C3" t="n">
-        <v>10.703</v>
+        <v>10.203</v>
       </c>
       <c r="D3" t="n">
         <v>0.204</v>
@@ -2761,17 +3838,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sensor 477</t>
+          <t>Sensor 573</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.385</v>
+        <v>0.526</v>
       </c>
       <c r="C4" t="n">
-        <v>6.853</v>
+        <v>8.84</v>
       </c>
       <c r="D4" t="n">
-        <v>0.228</v>
+        <v>0.226</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -2780,55 +3857,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sensor 573</t>
+          <t>Sensor 130</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.352</v>
+        <v>0.466</v>
       </c>
       <c r="C5" t="n">
-        <v>6.271</v>
+        <v>7.831</v>
       </c>
       <c r="D5" t="n">
-        <v>0.226</v>
+        <v>0.625</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sensor 130</t>
+          <t>Sensor 290</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.339</v>
+        <v>0.41</v>
       </c>
       <c r="C6" t="n">
-        <v>6.032</v>
+        <v>6.889</v>
       </c>
       <c r="D6" t="n">
-        <v>0.625</v>
+        <v>0.29</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sensor 307</t>
+          <t>Sensor 571</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.312</v>
+        <v>0.36</v>
       </c>
       <c r="C7" t="n">
-        <v>5.549</v>
+        <v>6.053</v>
       </c>
       <c r="D7" t="n">
-        <v>0.14</v>
+        <v>0.207</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -2837,17 +3914,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sensor 288</t>
+          <t>Sensor 477</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.264</v>
+        <v>0.339</v>
       </c>
       <c r="C8" t="n">
-        <v>4.704</v>
+        <v>5.708</v>
       </c>
       <c r="D8" t="n">
-        <v>0.205</v>
+        <v>0.228</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -2856,17 +3933,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sensor 443</t>
+          <t>Sensor 309</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.264</v>
+        <v>0.331</v>
       </c>
       <c r="C9" t="n">
-        <v>4.701</v>
+        <v>5.567</v>
       </c>
       <c r="D9" t="n">
-        <v>0.143</v>
+        <v>0.14</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -2879,10 +3956,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24</v>
+        <v>0.254</v>
       </c>
       <c r="C10" t="n">
-        <v>4.277</v>
+        <v>4.265</v>
       </c>
       <c r="D10" t="n">
         <v>0.123</v>
@@ -2894,17 +3971,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sensor 41</t>
+          <t>Sensor 443</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.237</v>
+        <v>0.227</v>
       </c>
       <c r="C11" t="n">
-        <v>4.228</v>
+        <v>3.826</v>
       </c>
       <c r="D11" t="n">
-        <v>0.295</v>
+        <v>0.143</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -2917,10 +3994,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.223</v>
+        <v>0.22</v>
       </c>
       <c r="C12" t="n">
-        <v>3.961</v>
+        <v>3.693</v>
       </c>
       <c r="D12" t="n">
         <v>0.052</v>
@@ -2932,17 +4009,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sensor 64</t>
+          <t>Sensor 288</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2</v>
+        <v>0.189</v>
       </c>
       <c r="C13" t="n">
-        <v>3.559</v>
+        <v>3.182</v>
       </c>
       <c r="D13" t="n">
-        <v>0.101</v>
+        <v>0.205</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -2951,17 +4028,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sensor 405</t>
+          <t>Sensor 28</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.182</v>
+        <v>0.168</v>
       </c>
       <c r="C14" t="n">
-        <v>3.245</v>
+        <v>2.824</v>
       </c>
       <c r="D14" t="n">
-        <v>0.272</v>
+        <v>0.159</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -2970,17 +4047,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sensor 575</t>
+          <t>Sensor 426</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.175</v>
+        <v>0.159</v>
       </c>
       <c r="C15" t="n">
-        <v>3.11</v>
+        <v>2.682</v>
       </c>
       <c r="D15" t="n">
-        <v>0.232</v>
+        <v>0.227</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -2989,20 +4066,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sensor 126</t>
+          <t>Sensor 64</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.16</v>
+        <v>0.152</v>
       </c>
       <c r="C16" t="n">
-        <v>2.845</v>
+        <v>2.563</v>
       </c>
       <c r="D16" t="n">
-        <v>0.532</v>
+        <v>0.101</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
